--- a/testdata/realdata/sites.xlsx
+++ b/testdata/realdata/sites.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,11 @@
           <t>区县</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -455,6 +460,11 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -477,6 +487,11 @@
           <t>讷河</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -495,6 +510,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -517,6 +537,11 @@
           <t>大同</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -535,6 +560,11 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -557,6 +587,11 @@
           <t>巴彦</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -575,6 +610,11 @@
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -593,6 +633,11 @@
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -615,6 +660,11 @@
           <t>方正</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -637,6 +687,11 @@
           <t>甘南</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -655,6 +710,11 @@
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -677,6 +737,11 @@
           <t>呼兰</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -695,6 +760,11 @@
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -717,6 +787,11 @@
           <t>林口</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -739,6 +814,11 @@
           <t>漠河</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -761,6 +841,11 @@
           <t>木兰</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -783,6 +868,11 @@
           <t>青冈</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -805,6 +895,11 @@
           <t>庆安</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -823,6 +918,11 @@
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -841,6 +941,11 @@
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -863,6 +968,11 @@
           <t>汤原</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -881,6 +991,11 @@
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -903,6 +1018,11 @@
           <t>绥棱</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -925,6 +1045,11 @@
           <t>塔河</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -947,6 +1072,11 @@
           <t>望奎</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -969,6 +1099,11 @@
           <t>通河</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -987,6 +1122,11 @@
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1009,6 +1149,11 @@
           <t>延寿</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1027,6 +1172,11 @@
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1049,6 +1199,11 @@
           <t>鄂伦春自治旗</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1071,6 +1226,11 @@
           <t>城子河</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1093,6 +1253,11 @@
           <t>爱民</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1115,6 +1280,11 @@
           <t>道里</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1137,6 +1307,11 @@
           <t>松北</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1159,6 +1334,11 @@
           <t>香坊</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1181,6 +1361,11 @@
           <t>南岗</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1203,6 +1388,11 @@
           <t>道外</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1225,6 +1415,11 @@
           <t>西安</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1247,6 +1442,11 @@
           <t>东安</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1269,6 +1469,11 @@
           <t>乌翠</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1291,6 +1496,11 @@
           <t>龙沙</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1313,6 +1523,11 @@
           <t>新兴</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1331,6 +1546,11 @@
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1349,6 +1569,11 @@
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1367,6 +1592,11 @@
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1389,6 +1619,11 @@
           <t>富裕</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1407,6 +1642,11 @@
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1429,6 +1669,11 @@
           <t>依安</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1451,6 +1696,11 @@
           <t>铁力</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1469,6 +1719,11 @@
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1487,6 +1742,11 @@
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1505,6 +1765,11 @@
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1523,6 +1788,11 @@
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1545,6 +1815,11 @@
           <t>阿城</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1567,6 +1842,11 @@
           <t>伊春</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1585,6 +1865,11 @@
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1603,6 +1888,11 @@
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1621,6 +1911,11 @@
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1639,6 +1934,11 @@
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1661,6 +1961,11 @@
           <t>安达</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1683,6 +1988,11 @@
           <t>肇东</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1705,6 +2015,11 @@
           <t>兰西</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1727,6 +2042,11 @@
           <t>铁锋</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1749,6 +2069,11 @@
           <t>昂昂溪</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1771,6 +2096,11 @@
           <t>梅里斯达斡尔族</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1793,6 +2123,11 @@
           <t>杜尔伯特蒙古族自治县 ᠳᠥᠷᠪᠡᠳ ᠮᠣᠩᠭᠣᠯ ᠥᠪᠡᠷᠲᠡᠭᠡᠨ ᠵᠠᠰᠠᠬᠤ ᠰᠢᠶᠠᠨ</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1815,6 +2150,11 @@
           <t>让胡路</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1837,6 +2177,11 @@
           <t>萨尔图</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1859,6 +2204,11 @@
           <t>肇源</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1881,6 +2231,11 @@
           <t>肇州</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1903,6 +2258,11 @@
           <t>平房</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1925,6 +2285,11 @@
           <t>尚志</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1947,6 +2312,11 @@
           <t>海林</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1969,6 +2339,11 @@
           <t>阳明</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1991,6 +2366,11 @@
           <t>穆棱</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2013,6 +2393,11 @@
           <t>麻山</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2035,6 +2420,11 @@
           <t>恒山</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2057,6 +2447,11 @@
           <t>岭东</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2079,6 +2474,11 @@
           <t>集贤</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2101,6 +2501,11 @@
           <t>郊</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2123,6 +2528,11 @@
           <t>勃利</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2141,6 +2551,11 @@
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2159,6 +2574,11 @@
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
